--- a/data/Mörel-Filet/investment_decision/Breiten_district_investment_decision.xlsx
+++ b/data/Mörel-Filet/investment_decision/Breiten_district_investment_decision.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,7 +680,7 @@
         <v>46023</v>
       </c>
       <c r="B7" t="n">
-        <v>0.04763041659452596</v>
+        <v>0.07546877670588237</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -694,19 +694,19 @@
         <v>2.221503388335994</v>
       </c>
       <c r="F7" t="n">
-        <v>0.04763041659452598</v>
+        <v>0.07546877670588237</v>
       </c>
       <c r="G7" t="n">
         <v>2.221503388335994</v>
       </c>
       <c r="H7" t="n">
-        <v>0.04763041659452595</v>
+        <v>0.07546877670588238</v>
       </c>
       <c r="I7" t="n">
         <v>0.6766358927611499</v>
       </c>
       <c r="J7" t="n">
-        <v>0.04763041659452596</v>
+        <v>0.07546877670588237</v>
       </c>
       <c r="K7" t="n">
         <v>0.6766358927611499</v>
@@ -717,7 +717,7 @@
         <v>47849</v>
       </c>
       <c r="B8" t="n">
-        <v>0.04799175430439033</v>
+        <v>0.0770073335499403</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -731,19 +731,19 @@
         <v>2.221503388335994</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04799175430439032</v>
+        <v>0.0772103790117647</v>
       </c>
       <c r="G8" t="n">
         <v>2.221503388335994</v>
       </c>
       <c r="H8" t="n">
-        <v>0.04799175430439033</v>
+        <v>0.07721469776041229</v>
       </c>
       <c r="I8" t="n">
         <v>1.004304416269545</v>
       </c>
       <c r="J8" t="n">
-        <v>0.04799175430439033</v>
+        <v>0.0772103790117647</v>
       </c>
       <c r="K8" t="n">
         <v>1.004304416269545</v>
@@ -754,7 +754,7 @@
         <v>49675</v>
       </c>
       <c r="B9" t="n">
-        <v>0.04847993938463959</v>
+        <v>0.08075323032686973</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -768,19 +768,19 @@
         <v>2.221503388335994</v>
       </c>
       <c r="F9" t="n">
-        <v>0.04847993938463964</v>
+        <v>0.08145669938516754</v>
       </c>
       <c r="G9" t="n">
         <v>2.221503388335994</v>
       </c>
       <c r="H9" t="n">
-        <v>0.04847993938463964</v>
+        <v>0.08253681971764705</v>
       </c>
       <c r="I9" t="n">
         <v>1.194925691373311</v>
       </c>
       <c r="J9" t="n">
-        <v>0.04847993938463964</v>
+        <v>0.08253681971764706</v>
       </c>
       <c r="K9" t="n">
         <v>1.194925691373311</v>
@@ -791,7 +791,7 @@
         <v>51502</v>
       </c>
       <c r="B10" t="n">
-        <v>0.04847993938463959</v>
+        <v>0.08253681971764706</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -805,19 +805,19 @@
         <v>2.221503388335994</v>
       </c>
       <c r="F10" t="n">
-        <v>0.04860350021693374</v>
+        <v>0.08253681971764706</v>
       </c>
       <c r="G10" t="n">
         <v>2.221503388335994</v>
       </c>
       <c r="H10" t="n">
-        <v>0.04859655921520321</v>
+        <v>0.08253681971764705</v>
       </c>
       <c r="I10" t="n">
         <v>1.318760613623838</v>
       </c>
       <c r="J10" t="n">
-        <v>0.04847993938463965</v>
+        <v>0.08253681971764706</v>
       </c>
       <c r="K10" t="n">
         <v>1.318760613623838</v>
@@ -828,7 +828,7 @@
         <v>53328</v>
       </c>
       <c r="B11" t="n">
-        <v>0.04873209585538107</v>
+        <v>0.08253681971764705</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -842,19 +842,19 @@
         <v>2.221503388335994</v>
       </c>
       <c r="F11" t="n">
-        <v>0.04884622950008881</v>
+        <v>0.08253681971764705</v>
       </c>
       <c r="G11" t="n">
         <v>2.221503388335994</v>
       </c>
       <c r="H11" t="n">
-        <v>0.04883817450078784</v>
+        <v>0.08227459970736925</v>
       </c>
       <c r="I11" t="n">
         <v>1.405436240531222</v>
       </c>
       <c r="J11" t="n">
-        <v>0.04871825871131879</v>
+        <v>0.08235472890057442</v>
       </c>
       <c r="K11" t="n">
         <v>1.405436240531222</v>
@@ -1043,746 +1043,6 @@
       </c>
       <c r="K16" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0.002004890411850598</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Breiten</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>175</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1.403961884756137</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.002004890411850599</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1.403961884756137</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.002004890411850598</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1.403961884756137</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.002004890411850599</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1.403961884756137</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="n">
-        <v>47849</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0.002121208635629272</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Breiten</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>175</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1.403961884756137</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.002121208635629272</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1.403961884756137</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.002021408707158684</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1.403961884756137</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.002121208635629272</v>
-      </c>
-      <c r="K18" t="n">
-        <v>1.403961884756137</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>49675</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0.002215111983830486</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Breiten</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>175</v>
-      </c>
-      <c r="E19" t="n">
-        <v>1.403961884756137</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.002273985998147566</v>
-      </c>
-      <c r="G19" t="n">
-        <v>1.403961884756137</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.002273985998147566</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1.403961884756137</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.002215111983830484</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1.403961884756137</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="n">
-        <v>51502</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0.002390742011176672</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Breiten</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>175</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1.403961884756137</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.00238540992721482</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1.403961884756137</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.002384909031679899</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1.403961884756137</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.002389966868456132</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1.403961884756137</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>53328</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0.002390742011176672</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Breiten</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>175</v>
-      </c>
-      <c r="E21" t="n">
-        <v>1.403961884756137</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.00238540992721482</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1.403961884756137</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.002384909031679899</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1.403961884756137</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.002389966868456132</v>
-      </c>
-      <c r="K21" t="n">
-        <v>1.403961884756137</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Breiten</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>8</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.1638445987293956</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.1638445987293956</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.004680920673646029</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.004680920673646029</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="n">
-        <v>47849</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Breiten</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>8</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.1638445987293956</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.1638445987293956</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.008210713368621643</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0.008210713368621643</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="n">
-        <v>49675</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Breiten</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>8</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.1638445987293956</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.1638445987293956</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.01105592339254044</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0.01105592339254044</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="n">
-        <v>51502</v>
-      </c>
-      <c r="B25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Breiten</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>8</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.1638445987293956</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.1638445987293956</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.01345096016691924</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0.01345096016691924</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="n">
-        <v>53328</v>
-      </c>
-      <c r="B26" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Breiten</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>8</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.1638445987293956</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0.1638445987293956</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.01552526543852563</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0.01552526543852563</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Breiten</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.3158450095988349</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.3158450095988349</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.009023461539558611</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0.009023461539558611</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="n">
-        <v>47849</v>
-      </c>
-      <c r="B28" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Breiten</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.3158450095988349</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0.3158450095988349</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.01582788119252365</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0.01582788119252365</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="n">
-        <v>49675</v>
-      </c>
-      <c r="B29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Breiten</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.3158450095988349</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0.3158450095988349</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.02131262340730688</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0.02131262340730688</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="n">
-        <v>51502</v>
-      </c>
-      <c r="B30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Breiten</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.3158450095988349</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.3158450095988349</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.02592956176755516</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0.02592956176755516</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="n">
-        <v>53328</v>
-      </c>
-      <c r="B31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Breiten</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0.3158450095988349</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.3158450095988349</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.02992822253209759</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0.02992822253209759</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Breiten</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>300</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.004369189299450549</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0.004369189299450549</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0.0001248245512972275</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0.0001248245512972275</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="n">
-        <v>47849</v>
-      </c>
-      <c r="B33" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Breiten</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>300</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.004369189299450549</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0.004369189299450549</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.0002189523564965772</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0.0002189523564965772</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="n">
-        <v>49675</v>
-      </c>
-      <c r="B34" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Breiten</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>300</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.004369189299450549</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.004369189299450549</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0.0002948246238010785</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0.0002948246238010785</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="n">
-        <v>51502</v>
-      </c>
-      <c r="B35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Breiten</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>300</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.004369189299450549</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.004369189299450549</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.0003586922711178465</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0.0003586922711178465</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="n">
-        <v>53328</v>
-      </c>
-      <c r="B36" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Breiten</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>300</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.004369189299450549</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.004369189299450549</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0.0004140070783606834</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0.0004140070783606834</v>
       </c>
     </row>
   </sheetData>
